--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753489</v>
+        <v>122753488</v>
       </c>
       <c r="B105" t="n">
-        <v>89991</v>
+        <v>89995</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12199,14 +12199,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506267</v>
+        <v>506195</v>
       </c>
       <c r="R105" t="n">
-        <v>7130672</v>
+        <v>7130728</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753490</v>
+        <v>122753484</v>
       </c>
       <c r="B106" t="n">
-        <v>89991</v>
+        <v>89632</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12281,38 +12281,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506335</v>
+        <v>506158</v>
       </c>
       <c r="R106" t="n">
-        <v>7130604</v>
+        <v>7130894</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12375,10 +12375,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753492</v>
+        <v>122753491</v>
       </c>
       <c r="B107" t="n">
-        <v>78499</v>
+        <v>77694</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12391,34 +12391,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506432</v>
+        <v>506427</v>
       </c>
       <c r="R107" t="n">
-        <v>7130569</v>
+        <v>7130583</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753488</v>
+        <v>122753483</v>
       </c>
       <c r="B108" t="n">
-        <v>89991</v>
+        <v>78503</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12497,34 +12497,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506195</v>
+        <v>506148</v>
       </c>
       <c r="R108" t="n">
-        <v>7130728</v>
+        <v>7130977</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12557,6 +12557,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12587,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753486</v>
       </c>
       <c r="B109" t="n">
-        <v>77694</v>
+        <v>89995</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12603,34 +12608,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506206</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130920</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753485</v>
+        <v>122753490</v>
       </c>
       <c r="B110" t="n">
-        <v>78499</v>
+        <v>89995</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12709,34 +12714,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506188</v>
+        <v>506335</v>
       </c>
       <c r="R110" t="n">
-        <v>7130914</v>
+        <v>7130604</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12799,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753483</v>
+        <v>122753489</v>
       </c>
       <c r="B111" t="n">
-        <v>78499</v>
+        <v>89995</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12815,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506148</v>
+        <v>506267</v>
       </c>
       <c r="R111" t="n">
-        <v>7130977</v>
+        <v>7130672</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12875,11 +12880,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12910,10 +12910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753484</v>
+        <v>122753485</v>
       </c>
       <c r="B112" t="n">
-        <v>89628</v>
+        <v>78503</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12922,25 +12922,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>245044</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506158</v>
+        <v>506188</v>
       </c>
       <c r="R112" t="n">
-        <v>7130894</v>
+        <v>7130914</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753486</v>
+        <v>122753492</v>
       </c>
       <c r="B113" t="n">
-        <v>89991</v>
+        <v>78503</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13032,34 +13032,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506206</v>
+        <v>506432</v>
       </c>
       <c r="R113" t="n">
-        <v>7130920</v>
+        <v>7130569</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753488</v>
+        <v>122753483</v>
       </c>
       <c r="B105" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,34 +12179,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506195</v>
+        <v>506148</v>
       </c>
       <c r="R105" t="n">
-        <v>7130728</v>
+        <v>7130977</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12239,6 +12239,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12269,10 +12274,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753484</v>
+        <v>122753490</v>
       </c>
       <c r="B106" t="n">
-        <v>89632</v>
+        <v>89995</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12281,38 +12286,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>245044</v>
+        <v>1962</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506158</v>
+        <v>506335</v>
       </c>
       <c r="R106" t="n">
-        <v>7130894</v>
+        <v>7130604</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12481,10 +12486,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753483</v>
+        <v>122753489</v>
       </c>
       <c r="B108" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12497,34 +12502,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506148</v>
+        <v>506267</v>
       </c>
       <c r="R108" t="n">
-        <v>7130977</v>
+        <v>7130672</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12557,11 +12562,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12592,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753486</v>
+        <v>122753484</v>
       </c>
       <c r="B109" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12604,25 +12604,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12632,10 +12632,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506206</v>
+        <v>506158</v>
       </c>
       <c r="R109" t="n">
-        <v>7130920</v>
+        <v>7130894</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12698,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753490</v>
+        <v>122753485</v>
       </c>
       <c r="B110" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12714,34 +12714,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506335</v>
+        <v>506188</v>
       </c>
       <c r="R110" t="n">
-        <v>7130604</v>
+        <v>7130914</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753489</v>
+        <v>122753492</v>
       </c>
       <c r="B111" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506267</v>
+        <v>506432</v>
       </c>
       <c r="R111" t="n">
-        <v>7130672</v>
+        <v>7130569</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753485</v>
+        <v>122753486</v>
       </c>
       <c r="B112" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12926,21 +12926,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506188</v>
+        <v>506206</v>
       </c>
       <c r="R112" t="n">
-        <v>7130914</v>
+        <v>7130920</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753492</v>
+        <v>122753488</v>
       </c>
       <c r="B113" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13032,34 +13032,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506432</v>
+        <v>506195</v>
       </c>
       <c r="R113" t="n">
-        <v>7130569</v>
+        <v>7130728</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753483</v>
+        <v>122753486</v>
       </c>
       <c r="B105" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,21 +12179,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506148</v>
+        <v>506206</v>
       </c>
       <c r="R105" t="n">
-        <v>7130977</v>
+        <v>7130920</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12239,11 +12239,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12274,7 +12269,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753490</v>
+        <v>122753489</v>
       </c>
       <c r="B106" t="n">
         <v>89995</v>
@@ -12310,14 +12305,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506335</v>
+        <v>506267</v>
       </c>
       <c r="R106" t="n">
-        <v>7130604</v>
+        <v>7130672</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12380,10 +12375,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753491</v>
+        <v>122753485</v>
       </c>
       <c r="B107" t="n">
-        <v>77694</v>
+        <v>78503</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12396,34 +12391,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506427</v>
+        <v>506188</v>
       </c>
       <c r="R107" t="n">
-        <v>7130583</v>
+        <v>7130914</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12486,10 +12481,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753489</v>
+        <v>122753491</v>
       </c>
       <c r="B108" t="n">
-        <v>89995</v>
+        <v>77694</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12502,34 +12497,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506267</v>
+        <v>506427</v>
       </c>
       <c r="R108" t="n">
-        <v>7130672</v>
+        <v>7130583</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12698,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753485</v>
+        <v>122753490</v>
       </c>
       <c r="B110" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12714,34 +12709,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506188</v>
+        <v>506335</v>
       </c>
       <c r="R110" t="n">
-        <v>7130914</v>
+        <v>7130604</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12804,10 +12799,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753492</v>
+        <v>122753488</v>
       </c>
       <c r="B111" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12815,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506432</v>
+        <v>506195</v>
       </c>
       <c r="R111" t="n">
-        <v>7130569</v>
+        <v>7130728</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12910,10 +12905,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753486</v>
+        <v>122753492</v>
       </c>
       <c r="B112" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12926,34 +12921,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506206</v>
+        <v>506432</v>
       </c>
       <c r="R112" t="n">
-        <v>7130920</v>
+        <v>7130569</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13016,10 +13011,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753488</v>
+        <v>122753483</v>
       </c>
       <c r="B113" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13032,34 +13027,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506195</v>
+        <v>506148</v>
       </c>
       <c r="R113" t="n">
-        <v>7130728</v>
+        <v>7130977</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13092,6 +13087,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12587,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753484</v>
+        <v>122753490</v>
       </c>
       <c r="B109" t="n">
-        <v>89632</v>
+        <v>89995</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12599,38 +12599,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>245044</v>
+        <v>1962</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506158</v>
+        <v>506335</v>
       </c>
       <c r="R109" t="n">
-        <v>7130894</v>
+        <v>7130604</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753490</v>
+        <v>122753484</v>
       </c>
       <c r="B110" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12705,38 +12705,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506335</v>
+        <v>506158</v>
       </c>
       <c r="R110" t="n">
-        <v>7130604</v>
+        <v>7130894</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12587,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753490</v>
+        <v>122753484</v>
       </c>
       <c r="B109" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12599,38 +12599,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506335</v>
+        <v>506158</v>
       </c>
       <c r="R109" t="n">
-        <v>7130604</v>
+        <v>7130894</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753484</v>
+        <v>122753490</v>
       </c>
       <c r="B110" t="n">
-        <v>89632</v>
+        <v>89995</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12705,38 +12705,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245044</v>
+        <v>1962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506158</v>
+        <v>506335</v>
       </c>
       <c r="R110" t="n">
-        <v>7130894</v>
+        <v>7130604</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,7 +12163,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753486</v>
+        <v>122753490</v>
       </c>
       <c r="B105" t="n">
         <v>89995</v>
@@ -12199,14 +12199,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506206</v>
+        <v>506335</v>
       </c>
       <c r="R105" t="n">
-        <v>7130920</v>
+        <v>7130604</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12375,7 +12375,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753485</v>
+        <v>122753492</v>
       </c>
       <c r="B107" t="n">
         <v>78503</v>
@@ -12411,14 +12411,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506188</v>
+        <v>506432</v>
       </c>
       <c r="R107" t="n">
-        <v>7130914</v>
+        <v>7130569</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753491</v>
+        <v>122753488</v>
       </c>
       <c r="B108" t="n">
-        <v>77694</v>
+        <v>89995</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12497,34 +12497,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506427</v>
+        <v>506195</v>
       </c>
       <c r="R108" t="n">
-        <v>7130583</v>
+        <v>7130728</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12587,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753484</v>
+        <v>122753491</v>
       </c>
       <c r="B109" t="n">
-        <v>89632</v>
+        <v>77694</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12599,38 +12599,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>245044</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506158</v>
+        <v>506427</v>
       </c>
       <c r="R109" t="n">
-        <v>7130894</v>
+        <v>7130583</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753490</v>
+        <v>122753484</v>
       </c>
       <c r="B110" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12705,38 +12705,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506335</v>
+        <v>506158</v>
       </c>
       <c r="R110" t="n">
-        <v>7130604</v>
+        <v>7130894</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12799,10 +12799,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753488</v>
+        <v>122753483</v>
       </c>
       <c r="B111" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12815,34 +12815,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506195</v>
+        <v>506148</v>
       </c>
       <c r="R111" t="n">
-        <v>7130728</v>
+        <v>7130977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12875,6 +12875,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12905,7 +12910,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753492</v>
+        <v>122753485</v>
       </c>
       <c r="B112" t="n">
         <v>78503</v>
@@ -12941,14 +12946,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506432</v>
+        <v>506188</v>
       </c>
       <c r="R112" t="n">
-        <v>7130569</v>
+        <v>7130914</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13011,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753483</v>
+        <v>122753486</v>
       </c>
       <c r="B113" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13027,21 +13032,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13051,10 +13056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506148</v>
+        <v>506206</v>
       </c>
       <c r="R113" t="n">
-        <v>7130977</v>
+        <v>7130920</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13087,11 +13092,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753490</v>
+        <v>122753491</v>
       </c>
       <c r="B105" t="n">
-        <v>89995</v>
+        <v>77694</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,34 +12179,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506335</v>
+        <v>506427</v>
       </c>
       <c r="R105" t="n">
-        <v>7130604</v>
+        <v>7130583</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753489</v>
+        <v>122753484</v>
       </c>
       <c r="B106" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12281,38 +12281,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506267</v>
+        <v>506158</v>
       </c>
       <c r="R106" t="n">
-        <v>7130672</v>
+        <v>7130894</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12375,7 +12375,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753492</v>
+        <v>122753485</v>
       </c>
       <c r="B107" t="n">
         <v>78503</v>
@@ -12411,14 +12411,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506432</v>
+        <v>506188</v>
       </c>
       <c r="R107" t="n">
-        <v>7130569</v>
+        <v>7130914</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12587,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753489</v>
       </c>
       <c r="B109" t="n">
-        <v>77694</v>
+        <v>89995</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12603,34 +12603,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506267</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130672</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753484</v>
+        <v>122753486</v>
       </c>
       <c r="B110" t="n">
-        <v>89632</v>
+        <v>89995</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12705,25 +12705,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245044</v>
+        <v>1962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506158</v>
+        <v>506206</v>
       </c>
       <c r="R110" t="n">
-        <v>7130894</v>
+        <v>7130920</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12799,7 +12799,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753483</v>
+        <v>122753492</v>
       </c>
       <c r="B111" t="n">
         <v>78503</v>
@@ -12835,14 +12835,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506148</v>
+        <v>506432</v>
       </c>
       <c r="R111" t="n">
-        <v>7130977</v>
+        <v>7130569</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12875,11 +12875,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12910,7 +12905,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753485</v>
+        <v>122753483</v>
       </c>
       <c r="B112" t="n">
         <v>78503</v>
@@ -12950,10 +12945,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506188</v>
+        <v>506148</v>
       </c>
       <c r="R112" t="n">
-        <v>7130914</v>
+        <v>7130977</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12986,6 +12981,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13016,7 +13016,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753486</v>
+        <v>122753490</v>
       </c>
       <c r="B113" t="n">
         <v>89995</v>
@@ -13052,14 +13052,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506206</v>
+        <v>506335</v>
       </c>
       <c r="R113" t="n">
-        <v>7130920</v>
+        <v>7130604</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753491</v>
+        <v>122753490</v>
       </c>
       <c r="B105" t="n">
-        <v>77694</v>
+        <v>89995</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,34 +12179,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506427</v>
+        <v>506335</v>
       </c>
       <c r="R105" t="n">
-        <v>7130583</v>
+        <v>7130604</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753484</v>
+        <v>122753483</v>
       </c>
       <c r="B106" t="n">
-        <v>89632</v>
+        <v>78503</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12281,25 +12281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>245044</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506158</v>
+        <v>506148</v>
       </c>
       <c r="R106" t="n">
-        <v>7130894</v>
+        <v>7130977</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12345,6 +12345,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12375,10 +12380,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753485</v>
+        <v>122753488</v>
       </c>
       <c r="B107" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12391,34 +12396,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506188</v>
+        <v>506195</v>
       </c>
       <c r="R107" t="n">
-        <v>7130914</v>
+        <v>7130728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12481,10 +12486,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753488</v>
+        <v>122753485</v>
       </c>
       <c r="B108" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12497,34 +12502,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506195</v>
+        <v>506188</v>
       </c>
       <c r="R108" t="n">
-        <v>7130728</v>
+        <v>7130914</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12587,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753489</v>
+        <v>122753491</v>
       </c>
       <c r="B109" t="n">
-        <v>89995</v>
+        <v>77694</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12603,34 +12608,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506267</v>
+        <v>506427</v>
       </c>
       <c r="R109" t="n">
-        <v>7130672</v>
+        <v>7130583</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753486</v>
+        <v>122753484</v>
       </c>
       <c r="B110" t="n">
-        <v>89995</v>
+        <v>89632</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12705,25 +12710,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12733,10 +12738,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506206</v>
+        <v>506158</v>
       </c>
       <c r="R110" t="n">
-        <v>7130920</v>
+        <v>7130894</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12905,10 +12910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753483</v>
+        <v>122753486</v>
       </c>
       <c r="B112" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12921,21 +12926,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12945,10 +12950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506148</v>
+        <v>506206</v>
       </c>
       <c r="R112" t="n">
-        <v>7130977</v>
+        <v>7130920</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12981,11 +12986,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13016,7 +13016,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753490</v>
+        <v>122753489</v>
       </c>
       <c r="B113" t="n">
         <v>89995</v>
@@ -13052,14 +13052,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506335</v>
+        <v>506267</v>
       </c>
       <c r="R113" t="n">
-        <v>7130604</v>
+        <v>7130672</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,7 +12163,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753490</v>
+        <v>122753488</v>
       </c>
       <c r="B105" t="n">
         <v>89995</v>
@@ -12199,14 +12199,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506335</v>
+        <v>506195</v>
       </c>
       <c r="R105" t="n">
-        <v>7130604</v>
+        <v>7130728</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,7 +12269,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753483</v>
+        <v>122753492</v>
       </c>
       <c r="B106" t="n">
         <v>78503</v>
@@ -12305,14 +12305,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506148</v>
+        <v>506432</v>
       </c>
       <c r="R106" t="n">
-        <v>7130977</v>
+        <v>7130569</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12345,11 +12345,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12380,10 +12375,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753488</v>
+        <v>122753485</v>
       </c>
       <c r="B107" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12396,34 +12391,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506195</v>
+        <v>506188</v>
       </c>
       <c r="R107" t="n">
-        <v>7130728</v>
+        <v>7130914</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12486,10 +12481,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753485</v>
+        <v>122753490</v>
       </c>
       <c r="B108" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12502,34 +12497,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506188</v>
+        <v>506335</v>
       </c>
       <c r="R108" t="n">
-        <v>7130914</v>
+        <v>7130604</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12592,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753483</v>
       </c>
       <c r="B109" t="n">
-        <v>77694</v>
+        <v>78503</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12608,34 +12603,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506148</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130977</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12668,6 +12663,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753492</v>
+        <v>122753491</v>
       </c>
       <c r="B111" t="n">
-        <v>78503</v>
+        <v>77694</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506432</v>
+        <v>506427</v>
       </c>
       <c r="R111" t="n">
-        <v>7130569</v>
+        <v>7130583</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753488</v>
+        <v>122753483</v>
       </c>
       <c r="B105" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,34 +12179,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506195</v>
+        <v>506148</v>
       </c>
       <c r="R105" t="n">
-        <v>7130728</v>
+        <v>7130977</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12239,6 +12239,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12269,10 +12274,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753492</v>
+        <v>122753490</v>
       </c>
       <c r="B106" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12285,34 +12290,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506432</v>
+        <v>506335</v>
       </c>
       <c r="R106" t="n">
-        <v>7130569</v>
+        <v>7130604</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12375,10 +12380,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753485</v>
+        <v>122753488</v>
       </c>
       <c r="B107" t="n">
-        <v>78503</v>
+        <v>89995</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12391,34 +12396,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506188</v>
+        <v>506195</v>
       </c>
       <c r="R107" t="n">
-        <v>7130914</v>
+        <v>7130728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12481,7 +12486,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753490</v>
+        <v>122753489</v>
       </c>
       <c r="B108" t="n">
         <v>89995</v>
@@ -12517,14 +12522,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506335</v>
+        <v>506267</v>
       </c>
       <c r="R108" t="n">
-        <v>7130604</v>
+        <v>7130672</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12587,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753483</v>
+        <v>122753484</v>
       </c>
       <c r="B109" t="n">
-        <v>78503</v>
+        <v>89632</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12599,25 +12604,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>245044</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12627,10 +12632,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506148</v>
+        <v>506158</v>
       </c>
       <c r="R109" t="n">
-        <v>7130977</v>
+        <v>7130894</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12663,11 +12668,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12698,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753484</v>
+        <v>122753485</v>
       </c>
       <c r="B110" t="n">
-        <v>89632</v>
+        <v>78503</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12710,25 +12710,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245044</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12738,10 +12738,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506158</v>
+        <v>506188</v>
       </c>
       <c r="R110" t="n">
-        <v>7130894</v>
+        <v>7130914</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753489</v>
+        <v>122753492</v>
       </c>
       <c r="B113" t="n">
-        <v>89995</v>
+        <v>78503</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13032,34 +13032,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506267</v>
+        <v>506432</v>
       </c>
       <c r="R113" t="n">
-        <v>7130672</v>
+        <v>7130569</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12592,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753484</v>
+        <v>122753491</v>
       </c>
       <c r="B109" t="n">
-        <v>89632</v>
+        <v>77694</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12604,38 +12604,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>245044</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506158</v>
+        <v>506427</v>
       </c>
       <c r="R109" t="n">
-        <v>7130894</v>
+        <v>7130583</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12698,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753485</v>
+        <v>122753484</v>
       </c>
       <c r="B110" t="n">
-        <v>78503</v>
+        <v>89632</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12710,25 +12710,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>245044</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12738,10 +12738,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506188</v>
+        <v>506158</v>
       </c>
       <c r="R110" t="n">
-        <v>7130914</v>
+        <v>7130894</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753491</v>
+        <v>122753485</v>
       </c>
       <c r="B111" t="n">
-        <v>77694</v>
+        <v>78503</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506427</v>
+        <v>506188</v>
       </c>
       <c r="R111" t="n">
-        <v>7130583</v>
+        <v>7130914</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12592,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753484</v>
       </c>
       <c r="B109" t="n">
-        <v>77694</v>
+        <v>89632</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12604,38 +12604,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>245044</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506158</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130894</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12698,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753484</v>
+        <v>122753485</v>
       </c>
       <c r="B110" t="n">
-        <v>89632</v>
+        <v>78503</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12710,25 +12710,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245044</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12738,10 +12738,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506158</v>
+        <v>506188</v>
       </c>
       <c r="R110" t="n">
-        <v>7130894</v>
+        <v>7130914</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753485</v>
+        <v>122753491</v>
       </c>
       <c r="B111" t="n">
-        <v>78503</v>
+        <v>77694</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506188</v>
+        <v>506427</v>
       </c>
       <c r="R111" t="n">
-        <v>7130914</v>
+        <v>7130583</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753483</v>
+        <v>122753484</v>
       </c>
       <c r="B105" t="n">
-        <v>78503</v>
+        <v>89635</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12175,25 +12175,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>245044</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506148</v>
+        <v>506158</v>
       </c>
       <c r="R105" t="n">
-        <v>7130977</v>
+        <v>7130894</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12239,11 +12239,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12274,10 +12269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753490</v>
+        <v>122753492</v>
       </c>
       <c r="B106" t="n">
-        <v>89995</v>
+        <v>78506</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12290,34 +12285,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506335</v>
+        <v>506432</v>
       </c>
       <c r="R106" t="n">
-        <v>7130604</v>
+        <v>7130569</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12383,7 +12378,7 @@
         <v>122753488</v>
       </c>
       <c r="B107" t="n">
-        <v>89995</v>
+        <v>89998</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12486,10 +12481,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753489</v>
+        <v>122753485</v>
       </c>
       <c r="B108" t="n">
-        <v>89995</v>
+        <v>78506</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12502,34 +12497,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506267</v>
+        <v>506188</v>
       </c>
       <c r="R108" t="n">
-        <v>7130672</v>
+        <v>7130914</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12592,10 +12587,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753490</v>
       </c>
       <c r="B109" t="n">
-        <v>77694</v>
+        <v>89998</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12608,34 +12603,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506335</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130604</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12698,10 +12693,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753484</v>
+        <v>122753483</v>
       </c>
       <c r="B110" t="n">
-        <v>89632</v>
+        <v>78506</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12710,25 +12705,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>245044</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12738,10 +12733,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506158</v>
+        <v>506148</v>
       </c>
       <c r="R110" t="n">
-        <v>7130894</v>
+        <v>7130977</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12774,6 +12769,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753485</v>
+        <v>122753491</v>
       </c>
       <c r="B111" t="n">
-        <v>78503</v>
+        <v>77697</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506188</v>
+        <v>506427</v>
       </c>
       <c r="R111" t="n">
-        <v>7130914</v>
+        <v>7130583</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753486</v>
+        <v>122753489</v>
       </c>
       <c r="B112" t="n">
-        <v>89995</v>
+        <v>89998</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12946,14 +12946,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506206</v>
+        <v>506267</v>
       </c>
       <c r="R112" t="n">
-        <v>7130920</v>
+        <v>7130672</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753492</v>
+        <v>122753486</v>
       </c>
       <c r="B113" t="n">
-        <v>78503</v>
+        <v>89998</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13032,34 +13032,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506432</v>
+        <v>506206</v>
       </c>
       <c r="R113" t="n">
-        <v>7130569</v>
+        <v>7130920</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12163,10 +12163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753484</v>
+        <v>122753486</v>
       </c>
       <c r="B105" t="n">
-        <v>89635</v>
+        <v>90000</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12175,25 +12175,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>245044</v>
+        <v>1962</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506158</v>
+        <v>506206</v>
       </c>
       <c r="R105" t="n">
-        <v>7130894</v>
+        <v>7130920</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753492</v>
+        <v>122753483</v>
       </c>
       <c r="B106" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12305,14 +12305,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506432</v>
+        <v>506148</v>
       </c>
       <c r="R106" t="n">
-        <v>7130569</v>
+        <v>7130977</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12345,6 +12345,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12375,10 +12380,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753488</v>
+        <v>122753492</v>
       </c>
       <c r="B107" t="n">
-        <v>89998</v>
+        <v>78508</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12391,34 +12396,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506195</v>
+        <v>506432</v>
       </c>
       <c r="R107" t="n">
-        <v>7130728</v>
+        <v>7130569</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12481,10 +12486,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753485</v>
+        <v>122753488</v>
       </c>
       <c r="B108" t="n">
-        <v>78506</v>
+        <v>90000</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12497,34 +12502,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506188</v>
+        <v>506195</v>
       </c>
       <c r="R108" t="n">
-        <v>7130914</v>
+        <v>7130728</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12587,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753490</v>
+        <v>122753491</v>
       </c>
       <c r="B109" t="n">
-        <v>89998</v>
+        <v>77699</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12603,34 +12608,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506335</v>
+        <v>506427</v>
       </c>
       <c r="R109" t="n">
-        <v>7130604</v>
+        <v>7130583</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12693,10 +12698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753483</v>
+        <v>122753490</v>
       </c>
       <c r="B110" t="n">
-        <v>78506</v>
+        <v>90000</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12709,34 +12714,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506148</v>
+        <v>506335</v>
       </c>
       <c r="R110" t="n">
-        <v>7130977</v>
+        <v>7130604</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12769,11 +12774,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12804,10 +12804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122753491</v>
+        <v>122753485</v>
       </c>
       <c r="B111" t="n">
-        <v>77697</v>
+        <v>78508</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12820,34 +12820,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506427</v>
+        <v>506188</v>
       </c>
       <c r="R111" t="n">
-        <v>7130583</v>
+        <v>7130914</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122753489</v>
+        <v>122753484</v>
       </c>
       <c r="B112" t="n">
-        <v>89998</v>
+        <v>89637</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12922,38 +12922,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>245044</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergtjärnen Ö, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>506267</v>
+        <v>506158</v>
       </c>
       <c r="R112" t="n">
-        <v>7130672</v>
+        <v>7130894</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13016,10 +13016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122753486</v>
+        <v>122753489</v>
       </c>
       <c r="B113" t="n">
-        <v>89998</v>
+        <v>90000</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13052,14 +13052,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>506206</v>
+        <v>506267</v>
       </c>
       <c r="R113" t="n">
-        <v>7130920</v>
+        <v>7130672</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -12380,10 +12380,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753492</v>
+        <v>122753488</v>
       </c>
       <c r="B107" t="n">
-        <v>78508</v>
+        <v>90000</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12396,34 +12396,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506432</v>
+        <v>506195</v>
       </c>
       <c r="R107" t="n">
-        <v>7130569</v>
+        <v>7130728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12486,10 +12486,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753488</v>
+        <v>122753491</v>
       </c>
       <c r="B108" t="n">
-        <v>90000</v>
+        <v>77699</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12502,34 +12502,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506195</v>
+        <v>506427</v>
       </c>
       <c r="R108" t="n">
-        <v>7130728</v>
+        <v>7130583</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12592,10 +12592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753491</v>
+        <v>122753492</v>
       </c>
       <c r="B109" t="n">
-        <v>77699</v>
+        <v>78508</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12608,34 +12608,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506427</v>
+        <v>506432</v>
       </c>
       <c r="R109" t="n">
-        <v>7130583</v>
+        <v>7130569</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 30021-2020 artfynd.xlsx
+++ b/artfynd/A 30021-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88782423</v>
+        <v>89602965</v>
       </c>
       <c r="B2" t="n">
         <v>78569</v>
@@ -709,22 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506194.0153245296</v>
+        <v>506194.0161985114</v>
       </c>
       <c r="R2" t="n">
-        <v>7130808.583572838</v>
+        <v>7130808.1495055</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,14 +780,18 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88782416</v>
+        <v>89602971</v>
       </c>
       <c r="B3" t="n">
         <v>77506</v>
@@ -825,22 +825,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506330.5355530845</v>
+        <v>506330.9702036845</v>
       </c>
       <c r="R3" t="n">
-        <v>7130573.152945523</v>
+        <v>7130573.153839914</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,14 +896,18 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88782419</v>
+        <v>89602966</v>
       </c>
       <c r="B4" t="n">
         <v>78570</v>
@@ -941,22 +941,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506218.4705920019</v>
+        <v>506218.0359665211</v>
       </c>
       <c r="R4" t="n">
-        <v>7130750.901182668</v>
+        <v>7130750.900304158</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1012,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89602965</v>
+        <v>93927980</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
+        <v>56395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,37 +1271,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506194.0161985114</v>
+        <v>506248.585778766</v>
       </c>
       <c r="R7" t="n">
-        <v>7130808.1495055</v>
+        <v>7130902.885486113</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1329,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1335,12 +1339,17 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,21 +1369,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89602971</v>
+        <v>93928000</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,37 +1392,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506330.9702036845</v>
+        <v>506309.799810979</v>
       </c>
       <c r="R8" t="n">
-        <v>7130573.153839914</v>
+        <v>7130722.871999606</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1449,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1451,7 +1459,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1465,6 +1473,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,21 +1485,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89602966</v>
+        <v>113679038</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
+        <v>79558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1508,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506218.0359665211</v>
+        <v>506091</v>
       </c>
       <c r="R9" t="n">
-        <v>7130750.900304158</v>
+        <v>7130763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,22 +1562,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,30 +1578,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93927980</v>
+        <v>113680274</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
+        <v>91597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,41 +1619,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506248.585778766</v>
+        <v>506162</v>
       </c>
       <c r="R10" t="n">
-        <v>7130902.885486113</v>
+        <v>7130889</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,27 +1673,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,24 +1691,33 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93928000</v>
+        <v>113680285</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
+        <v>91605</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,44 +1726,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506309.799810979</v>
+        <v>506333</v>
       </c>
       <c r="R11" t="n">
-        <v>7130722.871999606</v>
+        <v>7130598</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,22 +1784,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,29 +1798,37 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113679038</v>
+        <v>113679035</v>
       </c>
       <c r="B12" t="n">
-        <v>79558</v>
+        <v>79518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506091</v>
+        <v>506106</v>
       </c>
       <c r="R12" t="n">
-        <v>7130763</v>
+        <v>7130777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680274</v>
+        <v>113678998</v>
       </c>
       <c r="B13" t="n">
-        <v>91597</v>
+        <v>79587</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,25 +1948,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506162</v>
+        <v>506374</v>
       </c>
       <c r="R13" t="n">
-        <v>7130889</v>
+        <v>7131127</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,12 +2023,12 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW13" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2062,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113680285</v>
+        <v>113679033</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>79558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,38 +2059,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>slåtten, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506333</v>
+        <v>506051</v>
       </c>
       <c r="R14" t="n">
-        <v>7130598</v>
+        <v>7130773</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,12 +2134,12 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW14" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2173,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113679035</v>
+        <v>113679054</v>
       </c>
       <c r="B15" t="n">
-        <v>79518</v>
+        <v>79559</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,25 +2170,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2213,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506106</v>
+        <v>506415</v>
       </c>
       <c r="R15" t="n">
-        <v>7130777</v>
+        <v>7130621</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113678998</v>
+        <v>113678976</v>
       </c>
       <c r="B16" t="n">
-        <v>79587</v>
+        <v>79558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,25 +2281,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506374</v>
+        <v>506389</v>
       </c>
       <c r="R16" t="n">
-        <v>7131127</v>
+        <v>7131021</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2369,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2395,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113679033</v>
+        <v>113679057</v>
       </c>
       <c r="B17" t="n">
-        <v>79558</v>
+        <v>78507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,34 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>slåtten, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506051</v>
+        <v>506424</v>
       </c>
       <c r="R17" t="n">
-        <v>7130773</v>
+        <v>7130585</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113679054</v>
+        <v>113678968</v>
       </c>
       <c r="B18" t="n">
-        <v>79559</v>
+        <v>79558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,21 +2507,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506415</v>
+        <v>506354</v>
       </c>
       <c r="R18" t="n">
-        <v>7130621</v>
+        <v>7130967</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2591,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2617,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113678976</v>
+        <v>113680242</v>
       </c>
       <c r="B19" t="n">
-        <v>79558</v>
+        <v>82248</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,21 +2618,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,7 +2645,7 @@
         <v>506389</v>
       </c>
       <c r="R19" t="n">
-        <v>7131021</v>
+        <v>7131119</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,12 +2689,12 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AS19" t="inlineStr">
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2717,7 +2702,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2728,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113679057</v>
+        <v>113680288</v>
       </c>
       <c r="B20" t="n">
-        <v>78507</v>
+        <v>91617</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,25 +2725,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2768,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506424</v>
+        <v>506392</v>
       </c>
       <c r="R20" t="n">
-        <v>7130585</v>
+        <v>7130626</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,12 +2800,12 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2839,7 +2824,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113678968</v>
+        <v>113679008</v>
       </c>
       <c r="B21" t="n">
         <v>79558</v>
@@ -2879,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506354</v>
+        <v>506137</v>
       </c>
       <c r="R21" t="n">
-        <v>7130967</v>
+        <v>7131095</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2924,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2950,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680242</v>
+        <v>113679028</v>
       </c>
       <c r="B22" t="n">
-        <v>82248</v>
+        <v>79559</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2990,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506389</v>
+        <v>506114</v>
       </c>
       <c r="R22" t="n">
-        <v>7131119</v>
+        <v>7130834</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3037,12 +3022,12 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW22" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3061,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680288</v>
+        <v>113679013</v>
       </c>
       <c r="B23" t="n">
-        <v>91617</v>
+        <v>79559</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,25 +3058,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506392</v>
+        <v>506127</v>
       </c>
       <c r="R23" t="n">
-        <v>7130626</v>
+        <v>7131075</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,12 +3133,12 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW23" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3172,10 +3157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113679008</v>
+        <v>113678974</v>
       </c>
       <c r="B24" t="n">
-        <v>79558</v>
+        <v>74647</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3188,21 +3173,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3212,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506137</v>
+        <v>506362</v>
       </c>
       <c r="R24" t="n">
-        <v>7131095</v>
+        <v>7131007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3272,7 +3257,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3283,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113679028</v>
+        <v>113678977</v>
       </c>
       <c r="B25" t="n">
-        <v>79559</v>
+        <v>79558</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,21 +3284,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506114</v>
+        <v>506394</v>
       </c>
       <c r="R25" t="n">
-        <v>7130834</v>
+        <v>7131019</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3383,7 +3368,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3394,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113679013</v>
+        <v>113679009</v>
       </c>
       <c r="B26" t="n">
-        <v>79559</v>
+        <v>79558</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,21 +3395,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3434,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506127</v>
+        <v>506121</v>
       </c>
       <c r="R26" t="n">
-        <v>7131075</v>
+        <v>7131091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3505,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113678974</v>
+        <v>113679011</v>
       </c>
       <c r="B27" t="n">
-        <v>74647</v>
+        <v>79558</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,21 +3506,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506362</v>
+        <v>506132</v>
       </c>
       <c r="R27" t="n">
-        <v>7131007</v>
+        <v>7131069</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3605,7 +3590,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3616,7 +3601,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113678977</v>
+        <v>113678983</v>
       </c>
       <c r="B28" t="n">
         <v>79558</v>
@@ -3656,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506394</v>
+        <v>506397</v>
       </c>
       <c r="R28" t="n">
-        <v>7131019</v>
+        <v>7131034</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113679009</v>
+        <v>113680286</v>
       </c>
       <c r="B29" t="n">
-        <v>79558</v>
+        <v>91621</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3743,21 +3728,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3767,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506121</v>
+        <v>506385</v>
       </c>
       <c r="R29" t="n">
-        <v>7131091</v>
+        <v>7130634</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,12 +3799,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3838,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113679011</v>
+        <v>113680238</v>
       </c>
       <c r="B30" t="n">
-        <v>79558</v>
+        <v>91621</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3854,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3878,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506132</v>
+        <v>506317</v>
       </c>
       <c r="R30" t="n">
-        <v>7131069</v>
+        <v>7130856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3925,12 +3910,12 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3949,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113678983</v>
+        <v>113680277</v>
       </c>
       <c r="B31" t="n">
-        <v>79558</v>
+        <v>91597</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,21 +3950,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3989,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506397</v>
+        <v>506144</v>
       </c>
       <c r="R31" t="n">
-        <v>7131034</v>
+        <v>7130838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,12 +4021,12 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4049,7 +4034,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4060,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113680286</v>
+        <v>113679020</v>
       </c>
       <c r="B32" t="n">
-        <v>91621</v>
+        <v>78157</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506385</v>
+        <v>506111</v>
       </c>
       <c r="R32" t="n">
-        <v>7130634</v>
+        <v>7131017</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4147,12 +4132,12 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW32" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4171,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113680238</v>
+        <v>113680248</v>
       </c>
       <c r="B33" t="n">
-        <v>91621</v>
+        <v>90297</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4183,25 +4168,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4211,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506317</v>
+        <v>506124</v>
       </c>
       <c r="R33" t="n">
-        <v>7130856</v>
+        <v>7131071</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4282,10 +4267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113680277</v>
+        <v>113680278</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>90350</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4298,21 +4283,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,10 +4307,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506144</v>
+        <v>506127</v>
       </c>
       <c r="R34" t="n">
-        <v>7130838</v>
+        <v>7130845</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113679020</v>
+        <v>113680273</v>
       </c>
       <c r="B35" t="n">
-        <v>78157</v>
+        <v>91621</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4409,21 +4394,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4433,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506111</v>
+        <v>506054</v>
       </c>
       <c r="R35" t="n">
-        <v>7131017</v>
+        <v>7130957</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4480,12 +4465,12 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4504,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113680248</v>
+        <v>113678984</v>
       </c>
       <c r="B36" t="n">
-        <v>90297</v>
+        <v>79559</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,25 +4501,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506124</v>
+        <v>506397</v>
       </c>
       <c r="R36" t="n">
-        <v>7131071</v>
+        <v>7131034</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,12 +4576,12 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW36" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4604,7 +4589,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4615,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113680278</v>
+        <v>113680280</v>
       </c>
       <c r="B37" t="n">
-        <v>90350</v>
+        <v>90346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4631,21 +4616,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4655,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506127</v>
+        <v>506151</v>
       </c>
       <c r="R37" t="n">
-        <v>7130845</v>
+        <v>7130712</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4726,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113680273</v>
+        <v>113679030</v>
       </c>
       <c r="B38" t="n">
-        <v>91621</v>
+        <v>79558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4742,21 +4727,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4766,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506054</v>
+        <v>506116</v>
       </c>
       <c r="R38" t="n">
-        <v>7130957</v>
+        <v>7130836</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,12 +4798,12 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW38" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4837,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113678984</v>
+        <v>113682609</v>
       </c>
       <c r="B39" t="n">
-        <v>79559</v>
+        <v>97650</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4849,25 +4834,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4877,10 +4862,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506397</v>
+        <v>506124</v>
       </c>
       <c r="R39" t="n">
-        <v>7131034</v>
+        <v>7130828</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,7 +4922,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4948,10 +4933,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113680280</v>
+        <v>113680240</v>
       </c>
       <c r="B40" t="n">
-        <v>90346</v>
+        <v>90328</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4964,21 +4949,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4988,10 +4973,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506151</v>
+        <v>506392</v>
       </c>
       <c r="R40" t="n">
-        <v>7130712</v>
+        <v>7131056</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5059,10 +5044,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113679030</v>
+        <v>113680243</v>
       </c>
       <c r="B41" t="n">
-        <v>79558</v>
+        <v>82248</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5075,21 +5060,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5099,10 +5084,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506116</v>
+        <v>506385</v>
       </c>
       <c r="R41" t="n">
-        <v>7130836</v>
+        <v>7131115</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5146,12 +5131,12 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AS41" t="inlineStr">
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5170,10 +5155,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113682609</v>
+        <v>113680284</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
+        <v>82248</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5182,25 +5167,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5210,10 +5195,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506124</v>
+        <v>506337</v>
       </c>
       <c r="R42" t="n">
-        <v>7130828</v>
+        <v>7130578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5257,12 +5242,12 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AS42" t="inlineStr">
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5281,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113680240</v>
+        <v>113678987</v>
       </c>
       <c r="B43" t="n">
-        <v>90328</v>
+        <v>74647</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5297,21 +5282,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5321,10 +5306,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506392</v>
+        <v>506391</v>
       </c>
       <c r="R43" t="n">
-        <v>7131056</v>
+        <v>7131034</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5368,12 +5353,12 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW43" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5381,7 +5366,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5392,10 +5377,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113680243</v>
+        <v>113680255</v>
       </c>
       <c r="B44" t="n">
-        <v>82248</v>
+        <v>91617</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5404,38 +5389,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>slåtten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506385</v>
+        <v>505993</v>
       </c>
       <c r="R44" t="n">
-        <v>7131115</v>
+        <v>7130928</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5503,10 +5488,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113680284</v>
+        <v>113679047</v>
       </c>
       <c r="B45" t="n">
-        <v>82248</v>
+        <v>78157</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5504,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,10 +5528,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506337</v>
+        <v>506314</v>
       </c>
       <c r="R45" t="n">
-        <v>7130578</v>
+        <v>7130632</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5590,12 +5575,12 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW45" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5614,10 +5599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113678987</v>
+        <v>113678997</v>
       </c>
       <c r="B46" t="n">
-        <v>74647</v>
+        <v>79593</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5626,25 +5611,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5654,10 +5639,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506391</v>
+        <v>506359</v>
       </c>
       <c r="R46" t="n">
-        <v>7131034</v>
+        <v>7131127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5714,7 +5699,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5725,10 +5710,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113680255</v>
+        <v>113680252</v>
       </c>
       <c r="B47" t="n">
-        <v>91617</v>
+        <v>91649</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5737,25 +5722,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5765,10 +5750,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505993</v>
+        <v>505932</v>
       </c>
       <c r="R47" t="n">
-        <v>7130928</v>
+        <v>7131013</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113679047</v>
+        <v>113679003</v>
       </c>
       <c r="B48" t="n">
-        <v>78157</v>
+        <v>79559</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5852,21 +5837,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5876,10 +5861,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506314</v>
+        <v>506239</v>
       </c>
       <c r="R48" t="n">
-        <v>7130632</v>
+        <v>7131106</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5947,10 +5932,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113678997</v>
+        <v>113679023</v>
       </c>
       <c r="B49" t="n">
-        <v>79593</v>
+        <v>78157</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5959,25 +5944,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5987,10 +5972,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506359</v>
+        <v>506186</v>
       </c>
       <c r="R49" t="n">
-        <v>7131127</v>
+        <v>7130844</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6058,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113680252</v>
+        <v>113679058</v>
       </c>
       <c r="B50" t="n">
-        <v>91649</v>
+        <v>78157</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6074,34 +6059,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>slåtten, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505932</v>
+        <v>506426</v>
       </c>
       <c r="R50" t="n">
-        <v>7131013</v>
+        <v>7130583</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,12 +6130,12 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW50" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6169,10 +6154,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113679003</v>
+        <v>113679006</v>
       </c>
       <c r="B51" t="n">
-        <v>79559</v>
+        <v>79558</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6185,21 +6170,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6209,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506239</v>
+        <v>506183</v>
       </c>
       <c r="R51" t="n">
-        <v>7131106</v>
+        <v>7131083</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6280,10 +6265,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113679023</v>
+        <v>113679025</v>
       </c>
       <c r="B52" t="n">
-        <v>78157</v>
+        <v>79559</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6296,21 +6281,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6320,10 +6305,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506186</v>
+        <v>506137</v>
       </c>
       <c r="R52" t="n">
-        <v>7130844</v>
+        <v>7130828</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6391,10 +6376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113679058</v>
+        <v>113680275</v>
       </c>
       <c r="B53" t="n">
-        <v>78157</v>
+        <v>91621</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6407,21 +6392,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6431,10 +6416,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506426</v>
+        <v>506152</v>
       </c>
       <c r="R53" t="n">
-        <v>7130583</v>
+        <v>7130893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6478,12 +6463,12 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6502,10 +6487,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113679006</v>
+        <v>113682600</v>
       </c>
       <c r="B54" t="n">
-        <v>79558</v>
+        <v>97650</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6514,25 +6499,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6542,10 +6527,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506183</v>
+        <v>506403</v>
       </c>
       <c r="R54" t="n">
-        <v>7131083</v>
+        <v>7131035</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6613,10 +6598,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113679025</v>
+        <v>113682603</v>
       </c>
       <c r="B55" t="n">
-        <v>79559</v>
+        <v>97650</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6625,25 +6610,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6653,10 +6638,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506137</v>
+        <v>506118</v>
       </c>
       <c r="R55" t="n">
-        <v>7130828</v>
+        <v>7131076</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6724,10 +6709,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113680275</v>
+        <v>113678971</v>
       </c>
       <c r="B56" t="n">
-        <v>91621</v>
+        <v>74647</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6740,21 +6725,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6764,10 +6749,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506152</v>
+        <v>506357</v>
       </c>
       <c r="R56" t="n">
-        <v>7130893</v>
+        <v>7131006</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6811,12 +6796,12 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW56" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6824,7 +6809,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6835,10 +6820,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113682600</v>
+        <v>113678966</v>
       </c>
       <c r="B57" t="n">
-        <v>97650</v>
+        <v>78507</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6847,25 +6832,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6875,10 +6860,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506403</v>
+        <v>506353</v>
       </c>
       <c r="R57" t="n">
-        <v>7131035</v>
+        <v>7130841</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6935,7 +6920,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6946,10 +6931,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113682603</v>
+        <v>113678990</v>
       </c>
       <c r="B58" t="n">
-        <v>97650</v>
+        <v>79558</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6958,25 +6943,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6986,10 +6971,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506118</v>
+        <v>506411</v>
       </c>
       <c r="R58" t="n">
-        <v>7131076</v>
+        <v>7131072</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7046,7 +7031,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7057,10 +7042,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113678971</v>
+        <v>113678993</v>
       </c>
       <c r="B59" t="n">
-        <v>74647</v>
+        <v>78507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7073,21 +7058,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7097,10 +7082,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506357</v>
+        <v>506389</v>
       </c>
       <c r="R59" t="n">
-        <v>7131006</v>
+        <v>7131119</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7157,7 +7142,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7168,10 +7153,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113678966</v>
+        <v>113678995</v>
       </c>
       <c r="B60" t="n">
-        <v>78507</v>
+        <v>79559</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7184,21 +7169,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7208,10 +7193,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506353</v>
+        <v>506372</v>
       </c>
       <c r="R60" t="n">
-        <v>7130841</v>
+        <v>7131123</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7268,7 +7253,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7279,10 +7264,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113678990</v>
+        <v>113679052</v>
       </c>
       <c r="B61" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7295,21 +7280,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7319,10 +7304,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506411</v>
+        <v>506422</v>
       </c>
       <c r="R61" t="n">
-        <v>7131072</v>
+        <v>7130646</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7379,7 +7364,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7390,10 +7375,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113678993</v>
+        <v>113679046</v>
       </c>
       <c r="B62" t="n">
-        <v>78507</v>
+        <v>80429</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7406,21 +7391,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7430,10 +7415,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506389</v>
+        <v>506267</v>
       </c>
       <c r="R62" t="n">
-        <v>7131119</v>
+        <v>7130625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,10 +7486,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113678995</v>
+        <v>113679036</v>
       </c>
       <c r="B63" t="n">
-        <v>79559</v>
+        <v>79593</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7513,25 +7498,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7541,10 +7526,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506372</v>
+        <v>506088</v>
       </c>
       <c r="R63" t="n">
-        <v>7131123</v>
+        <v>7130761</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7612,10 +7597,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113679052</v>
+        <v>113679039</v>
       </c>
       <c r="B64" t="n">
-        <v>79559</v>
+        <v>79464</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7624,25 +7609,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7652,10 +7637,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506422</v>
+        <v>506094</v>
       </c>
       <c r="R64" t="n">
-        <v>7130646</v>
+        <v>7130757</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7723,10 +7708,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113679046</v>
+        <v>113679001</v>
       </c>
       <c r="B65" t="n">
-        <v>80429</v>
+        <v>79558</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7739,21 +7724,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7763,10 +7748,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506267</v>
+        <v>506239</v>
       </c>
       <c r="R65" t="n">
-        <v>7130625</v>
+        <v>7131107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7834,10 +7819,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113679036</v>
+        <v>113678970</v>
       </c>
       <c r="B66" t="n">
-        <v>79593</v>
+        <v>79559</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7846,25 +7831,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7874,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506088</v>
+        <v>506347</v>
       </c>
       <c r="R66" t="n">
-        <v>7130761</v>
+        <v>7130991</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,7 +7919,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7945,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113679039</v>
+        <v>113679042</v>
       </c>
       <c r="B67" t="n">
-        <v>79464</v>
+        <v>74647</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7957,25 +7942,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7985,10 +7970,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506094</v>
+        <v>506155</v>
       </c>
       <c r="R67" t="n">
-        <v>7130757</v>
+        <v>7130722</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8056,10 +8041,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113679001</v>
+        <v>113679053</v>
       </c>
       <c r="B68" t="n">
-        <v>79558</v>
+        <v>79464</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8068,25 +8053,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8096,10 +8081,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506239</v>
+        <v>506420</v>
       </c>
       <c r="R68" t="n">
-        <v>7131107</v>
+        <v>7130636</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8167,10 +8152,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113678970</v>
+        <v>113679027</v>
       </c>
       <c r="B69" t="n">
-        <v>79559</v>
+        <v>79593</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8179,25 +8164,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8207,10 +8192,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506347</v>
+        <v>506114</v>
       </c>
       <c r="R69" t="n">
-        <v>7130991</v>
+        <v>7130834</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8267,7 +8252,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8278,10 +8263,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113679042</v>
+        <v>113682610</v>
       </c>
       <c r="B70" t="n">
-        <v>74647</v>
+        <v>97650</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8290,25 +8275,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8318,10 +8303,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506155</v>
+        <v>506117</v>
       </c>
       <c r="R70" t="n">
-        <v>7130722</v>
+        <v>7130832</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8389,10 +8374,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113679053</v>
+        <v>113679043</v>
       </c>
       <c r="B71" t="n">
-        <v>79464</v>
+        <v>74640</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8401,25 +8386,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8429,10 +8414,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506420</v>
+        <v>506272</v>
       </c>
       <c r="R71" t="n">
-        <v>7130636</v>
+        <v>7130701</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8500,10 +8485,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113679027</v>
+        <v>113680241</v>
       </c>
       <c r="B72" t="n">
-        <v>79593</v>
+        <v>82248</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8512,25 +8497,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8540,10 +8525,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506114</v>
+        <v>506362</v>
       </c>
       <c r="R72" t="n">
-        <v>7130834</v>
+        <v>7131084</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8587,12 +8572,12 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8611,10 +8596,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113682610</v>
+        <v>113680246</v>
       </c>
       <c r="B73" t="n">
-        <v>97650</v>
+        <v>90332</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8623,25 +8608,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8651,10 +8636,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506117</v>
+        <v>506382</v>
       </c>
       <c r="R73" t="n">
-        <v>7130832</v>
+        <v>7131133</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8698,12 +8683,12 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8722,10 +8707,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113679043</v>
+        <v>113679048</v>
       </c>
       <c r="B74" t="n">
-        <v>74640</v>
+        <v>79099</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8738,21 +8723,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8762,10 +8747,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506272</v>
+        <v>506305</v>
       </c>
       <c r="R74" t="n">
-        <v>7130701</v>
+        <v>7130630</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8833,10 +8818,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113680241</v>
+        <v>113680276</v>
       </c>
       <c r="B75" t="n">
-        <v>82248</v>
+        <v>90297</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8845,25 +8830,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8873,10 +8858,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506362</v>
+        <v>506178</v>
       </c>
       <c r="R75" t="n">
-        <v>7131084</v>
+        <v>7130844</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8944,10 +8929,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113680246</v>
+        <v>113680279</v>
       </c>
       <c r="B76" t="n">
-        <v>90332</v>
+        <v>90316</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8956,25 +8941,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8984,10 +8969,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506382</v>
+        <v>506112</v>
       </c>
       <c r="R76" t="n">
-        <v>7131133</v>
+        <v>7130759</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9055,10 +9040,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113679048</v>
+        <v>113680237</v>
       </c>
       <c r="B77" t="n">
-        <v>79099</v>
+        <v>91621</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9071,21 +9056,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9095,10 +9080,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506305</v>
+        <v>506486</v>
       </c>
       <c r="R77" t="n">
-        <v>7130630</v>
+        <v>7130693</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9142,12 +9127,12 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9166,10 +9151,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113680276</v>
+        <v>113682601</v>
       </c>
       <c r="B78" t="n">
-        <v>90297</v>
+        <v>97650</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9178,25 +9163,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9206,10 +9191,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506178</v>
+        <v>506387</v>
       </c>
       <c r="R78" t="n">
-        <v>7130844</v>
+        <v>7131121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9253,12 +9238,12 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW78" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9277,10 +9262,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113680279</v>
+        <v>113679044</v>
       </c>
       <c r="B79" t="n">
-        <v>90316</v>
+        <v>78157</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9289,25 +9274,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4660</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9317,10 +9302,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506112</v>
+        <v>506256</v>
       </c>
       <c r="R79" t="n">
-        <v>7130759</v>
+        <v>7130608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9364,12 +9349,12 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9388,10 +9373,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>113680237</v>
+        <v>113679056</v>
       </c>
       <c r="B80" t="n">
-        <v>91621</v>
+        <v>78157</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9404,21 +9389,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9428,10 +9413,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506486</v>
+        <v>506443</v>
       </c>
       <c r="R80" t="n">
-        <v>7130693</v>
+        <v>7130603</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9475,12 +9460,12 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW80" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9499,10 +9484,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113682601</v>
+        <v>113679037</v>
       </c>
       <c r="B81" t="n">
-        <v>97650</v>
+        <v>79587</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9511,25 +9496,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9539,10 +9524,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506387</v>
+        <v>506087</v>
       </c>
       <c r="R81" t="n">
-        <v>7131121</v>
+        <v>7130759</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9610,10 +9595,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113679044</v>
+        <v>113678992</v>
       </c>
       <c r="B82" t="n">
-        <v>78157</v>
+        <v>79558</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9626,21 +9611,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9650,10 +9635,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506256</v>
+        <v>506406</v>
       </c>
       <c r="R82" t="n">
-        <v>7130608</v>
+        <v>7131128</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9721,10 +9706,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113679056</v>
+        <v>113680287</v>
       </c>
       <c r="B83" t="n">
-        <v>78157</v>
+        <v>91621</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9737,21 +9722,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9761,10 +9746,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506443</v>
+        <v>506393</v>
       </c>
       <c r="R83" t="n">
-        <v>7130603</v>
+        <v>7130628</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9808,12 +9793,12 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AS83" t="inlineStr">
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9832,10 +9817,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113679037</v>
+        <v>113678969</v>
       </c>
       <c r="B84" t="n">
-        <v>79587</v>
+        <v>74647</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9844,25 +9829,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9872,10 +9857,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506087</v>
+        <v>506347</v>
       </c>
       <c r="R84" t="n">
-        <v>7130759</v>
+        <v>7130978</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9932,7 +9917,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9943,10 +9928,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113678992</v>
+        <v>113680282</v>
       </c>
       <c r="B85" t="n">
-        <v>79558</v>
+        <v>90297</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9955,25 +9940,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9983,10 +9968,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506406</v>
+        <v>506254</v>
       </c>
       <c r="R85" t="n">
-        <v>7131128</v>
+        <v>7130622</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10030,12 +10015,12 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AS85" t="inlineStr">
+      <c r="AT85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -10054,10 +10039,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113680287</v>
+        <v>113679049</v>
       </c>
       <c r="B86" t="n">
-        <v>91621</v>
+        <v>74647</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10070,21 +10055,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2059</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10094,10 +10079,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506393</v>
+        <v>506310</v>
       </c>
       <c r="R86" t="n">
-        <v>7130628</v>
+        <v>7130567</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10141,12 +10126,12 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW86" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -10165,10 +10150,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113678969</v>
+        <v>113679005</v>
       </c>
       <c r="B87" t="n">
-        <v>74647</v>
+        <v>79558</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10181,21 +10166,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10205,10 +10190,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506347</v>
+        <v>506232</v>
       </c>
       <c r="R87" t="n">
-        <v>7130978</v>
+        <v>7131093</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10265,7 +10250,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10276,10 +10261,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113680282</v>
+        <v>113679034</v>
       </c>
       <c r="B88" t="n">
-        <v>90297</v>
+        <v>74647</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10288,25 +10273,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10316,10 +10301,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506254</v>
+        <v>506107</v>
       </c>
       <c r="R88" t="n">
-        <v>7130622</v>
+        <v>7130777</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10363,12 +10348,12 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT88" t="inlineStr"/>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW88" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -10387,10 +10372,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113679049</v>
+        <v>113679000</v>
       </c>
       <c r="B89" t="n">
-        <v>74647</v>
+        <v>79558</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10403,21 +10388,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10427,10 +10412,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506310</v>
+        <v>506318</v>
       </c>
       <c r="R89" t="n">
-        <v>7130567</v>
+        <v>7131117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10498,10 +10483,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113679005</v>
+        <v>113679051</v>
       </c>
       <c r="B90" t="n">
-        <v>79558</v>
+        <v>79594</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10510,25 +10495,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10538,10 +10523,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>506232</v>
+        <v>506420</v>
       </c>
       <c r="R90" t="n">
-        <v>7131093</v>
+        <v>7130646</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10609,10 +10594,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113679034</v>
+        <v>113682602</v>
       </c>
       <c r="B91" t="n">
-        <v>74647</v>
+        <v>97650</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10621,25 +10606,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10649,10 +10634,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>506107</v>
+        <v>506172</v>
       </c>
       <c r="R91" t="n">
-        <v>7130777</v>
+        <v>7131093</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10720,10 +10705,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113679000</v>
+        <v>113678988</v>
       </c>
       <c r="B92" t="n">
-        <v>79558</v>
+        <v>74632</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10732,25 +10717,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10760,10 +10745,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>506318</v>
+        <v>506393</v>
       </c>
       <c r="R92" t="n">
-        <v>7131117</v>
+        <v>7131048</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10820,7 +10805,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10831,10 +10816,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113679051</v>
+        <v>113680254</v>
       </c>
       <c r="B93" t="n">
-        <v>79594</v>
+        <v>91617</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10847,34 +10832,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>4366</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>slåtten, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>506420</v>
+        <v>506000</v>
       </c>
       <c r="R93" t="n">
-        <v>7130646</v>
+        <v>7130928</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10918,12 +10903,12 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AS93" t="inlineStr">
+      <c r="AT93" t="inlineStr"/>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -10942,10 +10927,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>113682602</v>
+        <v>113679050</v>
       </c>
       <c r="B94" t="n">
-        <v>97650</v>
+        <v>80429</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10954,25 +10939,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10982,10 +10967,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>506172</v>
+        <v>506330</v>
       </c>
       <c r="R94" t="n">
-        <v>7131093</v>
+        <v>7130596</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11053,10 +11038,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>113678988</v>
+        <v>113679022</v>
       </c>
       <c r="B95" t="n">
-        <v>74632</v>
+        <v>79074</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11065,25 +11050,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6439</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11093,10 +11078,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506393</v>
+        <v>506170</v>
       </c>
       <c r="R95" t="n">
-        <v>7131048</v>
+        <v>7130879</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11153,7 +11138,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11164,10 +11149,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>113680254</v>
+        <v>113678979</v>
       </c>
       <c r="B96" t="n">
-        <v>91617</v>
+        <v>79559</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11176,38 +11161,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4366</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>slåtten, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506000</v>
+        <v>506396</v>
       </c>
       <c r="R96" t="n">
-        <v>7130928</v>
+        <v>7131023</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11251,12 +11236,12 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW96" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -11264,7 +11249,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11275,10 +11260,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>113679050</v>
+        <v>113679055</v>
       </c>
       <c r="B97" t="n">
-        <v>80429</v>
+        <v>77895</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11291,21 +11276,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11315,10 +11300,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>506330</v>
+        <v>506403</v>
       </c>
       <c r="R97" t="n">
-        <v>7130596</v>
+        <v>7130597</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11386,10 +11371,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>113679022</v>
+        <v>113678973</v>
       </c>
       <c r="B98" t="n">
-        <v>79074</v>
+        <v>79558</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11402,21 +11387,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11426,10 +11411,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>506170</v>
+        <v>506361</v>
       </c>
       <c r="R98" t="n">
-        <v>7130879</v>
+        <v>7131004</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11486,7 +11471,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11497,10 +11482,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>113678979</v>
+        <v>113680239</v>
       </c>
       <c r="B99" t="n">
-        <v>79559</v>
+        <v>90297</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11509,25 +11494,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11537,10 +11522,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>506396</v>
+        <v>506388</v>
       </c>
       <c r="R99" t="n">
-        <v>7131023</v>
+        <v>7131024</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11584,12 +11569,12 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="AT99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -11597,7 +11582,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11608,10 +11593,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>113679055</v>
+        <v>113680283</v>
       </c>
       <c r="B100" t="n">
-        <v>77895</v>
+        <v>91617</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11620,25 +11605,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11648,10 +11633,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>506403</v>
+        <v>506270</v>
       </c>
       <c r="R100" t="n">
-        <v>7130597</v>
+        <v>7130623</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11695,12 +11680,12 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AT100" t="inlineStr"/>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -11719,10 +11704,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>113678973</v>
+        <v>113679031</v>
       </c>
       <c r="B101" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11735,34 +11720,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>slåtten, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>506361</v>
+        <v>506050</v>
       </c>
       <c r="R101" t="n">
-        <v>7131004</v>
+        <v>7130769</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11819,7 +11804,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11830,10 +11815,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>113680239</v>
+        <v>122753486</v>
       </c>
       <c r="B102" t="n">
-        <v>90297</v>
+        <v>90000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11842,38 +11827,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>506388</v>
+        <v>506206</v>
       </c>
       <c r="R102" t="n">
-        <v>7131024</v>
+        <v>7130920</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11918,19 +11903,14 @@
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
-      <c r="AU102" t="inlineStr">
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11941,10 +11921,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>113680283</v>
+        <v>122753483</v>
       </c>
       <c r="B103" t="n">
-        <v>91617</v>
+        <v>78508</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11953,38 +11933,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Långnäsbäcken, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>506270</v>
+        <v>506148</v>
       </c>
       <c r="R103" t="n">
-        <v>7130623</v>
+        <v>7130977</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12019,6 +11999,11 @@
           <t>2023-09-27</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På grov ketolåga.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12029,19 +12014,14 @@
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
-      <c r="AU103" t="inlineStr">
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AW103" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12052,10 +12032,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>113679031</v>
+        <v>122753488</v>
       </c>
       <c r="B104" t="n">
-        <v>79559</v>
+        <v>90000</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12068,34 +12048,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>slåtten, Jmt</t>
+          <t>Bergtjärnen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>506050</v>
+        <v>506195</v>
       </c>
       <c r="R104" t="n">
-        <v>7130769</v>
+        <v>7130728</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12139,11 +12119,6 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
@@ -12152,7 +12127,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12163,10 +12138,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122753486</v>
+        <v>122753491</v>
       </c>
       <c r="B105" t="n">
-        <v>90000</v>
+        <v>77699</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12179,34 +12154,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>506206</v>
+        <v>506427</v>
       </c>
       <c r="R105" t="n">
-        <v>7130920</v>
+        <v>7130583</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12269,7 +12244,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122753483</v>
+        <v>122753492</v>
       </c>
       <c r="B106" t="n">
         <v>78508</v>
@@ -12305,14 +12280,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Tretjärnavan V, Jmt</t>
+          <t>Torrkälen NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506148</v>
+        <v>506432</v>
       </c>
       <c r="R106" t="n">
-        <v>7130977</v>
+        <v>7130569</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12345,11 +12320,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På grov ketolåga.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12380,7 +12350,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122753488</v>
+        <v>122753490</v>
       </c>
       <c r="B107" t="n">
         <v>90000</v>
@@ -12416,14 +12386,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergtjärnen NÖ, Jmt</t>
+          <t>Rönbergstj. NV, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>506195</v>
+        <v>506335</v>
       </c>
       <c r="R107" t="n">
-        <v>7130728</v>
+        <v>7130604</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12486,10 +12456,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122753491</v>
+        <v>122753485</v>
       </c>
       <c r="B108" t="n">
-        <v>77699</v>
+        <v>78508</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12502,34 +12472,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506427</v>
+        <v>506188</v>
       </c>
       <c r="R108" t="n">
-        <v>7130583</v>
+        <v>7130914</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12592,10 +12562,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122753492</v>
+        <v>122753484</v>
       </c>
       <c r="B109" t="n">
-        <v>78508</v>
+        <v>89637</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12604,38 +12574,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>245044</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Torrkälen NÖ, Jmt</t>
+          <t>Tretjärnavan V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506432</v>
+        <v>506158</v>
       </c>
       <c r="R109" t="n">
-        <v>7130569</v>
+        <v>7130894</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12698,7 +12668,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122753490</v>
+        <v>122753489</v>
       </c>
       <c r="B110" t="n">
         <v>90000</v>
@@ -12734,14 +12704,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Rönbergstj. NV, Jmt</t>
+          <t>Bergtjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506335</v>
+        <v>506267</v>
       </c>
       <c r="R110" t="n">
-        <v>7130604</v>
+        <v>7130672</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12797,324 +12767,6 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>122753485</v>
-      </c>
-      <c r="B111" t="n">
-        <v>78508</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Tretjärnavan V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q111" t="n">
-        <v>506188</v>
-      </c>
-      <c r="R111" t="n">
-        <v>7130914</v>
-      </c>
-      <c r="S111" t="n">
-        <v>10</v>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AD111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="inlineStr"/>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>122753484</v>
-      </c>
-      <c r="B112" t="n">
-        <v>89637</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>245044</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Tallmusseron</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Tricholoma roseoacerbum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>A.Riva</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Tretjärnavan V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>506158</v>
-      </c>
-      <c r="R112" t="n">
-        <v>7130894</v>
-      </c>
-      <c r="S112" t="n">
-        <v>10</v>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AD112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT112" t="inlineStr"/>
-      <c r="AW112" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>122753489</v>
-      </c>
-      <c r="B113" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Bergtjärnen Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>506267</v>
-      </c>
-      <c r="R113" t="n">
-        <v>7130672</v>
-      </c>
-      <c r="S113" t="n">
-        <v>10</v>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AD113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT113" t="inlineStr"/>
-      <c r="AW113" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
         <is>
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
